--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488250_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488250_PROCESSED_CHRONO.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. VINCENT MAGO</t>
+          <t>E. COELHO PAULINO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0036</v>
+        <v>0.6323</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8425</v>
+        <v>-0.3044</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8389</v>
+        <v>0.9368</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7209</v>
+        <v>-0.5196</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4676</v>
+        <v>-1.131</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2533</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3811</v>
+        <v>-0.4534</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5884</v>
+        <v>-1.2413</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2074</v>
+        <v>0.788</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3398</v>
+        <v>-0.0663</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8791</v>
+        <v>0.1103</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4607</v>
+        <v>-0.1766</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5403</v>
+        <v>-0.2192</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1512</v>
+        <v>0.1489</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6108</v>
+        <v>-0.3681</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0011</v>
+        <v>0.63</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0011</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. COELHO PAULINO</t>
+          <t>A. RODRIGUEZ ESTRADA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8052</v>
+        <v>-0.4294</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4024</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2076</v>
+        <v>-0.4294</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5196</v>
+        <v>-0.2989</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.131</v>
+        <v>-0.4294</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.1306</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4534</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2413</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.788</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0663</v>
+        <v>-0.2989</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1103</v>
+        <v>-0.4294</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1766</v>
+        <v>0.1306</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0463</v>
+        <v>-0.1306</v>
       </c>
       <c r="T4" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0973</v>
+        <v>-0.1306</v>
       </c>
       <c r="V4" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>R. VINCENT MAGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4344</v>
+        <v>-1.1755</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1542</v>
+        <v>-0.3119</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7198</v>
+        <v>-0.8636</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3505</v>
+        <v>-1.7209</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2339</v>
+        <v>-1.4676</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1166</v>
+        <v>-0.2533</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8946</v>
+        <v>-0.3811</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8116</v>
+        <v>-0.5884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0829</v>
+        <v>0.2074</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2451</v>
+        <v>-1.3398</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0455</v>
+        <v>-0.8791</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1996</v>
+        <v>-0.4607</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.4823</v>
+        <v>0.1853</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S5" t="n">
-        <v>3.841</v>
+        <v>0.3613</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>0.9967</v>
       </c>
       <c r="U5" t="n">
-        <v>1.431</v>
+        <v>-0.6355</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5738</v>
+        <v>-0.0011</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6289</v>
+        <v>-0.0011</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ ESTRADA</t>
+          <t>F. QUINTERO DE ARMAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4294</v>
+        <v>-1.5096</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4294</v>
+        <v>-2.0514</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2989</v>
+        <v>-1.0053</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4294</v>
+        <v>-0.9807</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1306</v>
+        <v>-0.0246</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.6742</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.6742</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2989</v>
+        <v>-1.6796</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4294</v>
+        <v>-0.9807</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1306</v>
+        <v>-0.6989</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1306</v>
+        <v>-0.6895</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.1324</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1306</v>
+        <v>-0.5571</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. QUINTERO DE ARMAS</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7301</v>
+        <v>-2.0644</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3459</v>
+        <v>0.2136</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.076</v>
+        <v>-2.2781</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0053</v>
+        <v>1.6449</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9807</v>
+        <v>1.539</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0246</v>
+        <v>0.1059</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6742</v>
+        <v>3.1387</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.1174</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6742</v>
+        <v>0.0214</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6796</v>
+        <v>-1.4938</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9807</v>
+        <v>-1.5784</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6989</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1853</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1853</v>
+        <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.91</v>
+        <v>0.2907</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3283</v>
+        <v>-0.1458</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5817</v>
+        <v>0.4365</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4802</v>
+        <v>-2.1895</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.276</v>
+        <v>0.2935</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2042</v>
+        <v>-2.4831</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6449</v>
+        <v>-0.3505</v>
       </c>
       <c r="H8" t="n">
-        <v>1.539</v>
+        <v>-0.2339</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1059</v>
+        <v>-0.1166</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1387</v>
+        <v>1.8946</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1174</v>
+        <v>1.8116</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0214</v>
+        <v>0.0829</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4938</v>
+        <v>-2.2451</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5784</v>
+        <v>-2.0455</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.1996</v>
       </c>
       <c r="P8" t="n">
         <v>-1.4823</v>
@@ -1078,22 +1078,22 @@
         <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1251</v>
+        <v>1.2171</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6354</v>
+        <v>0.5494</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5103</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.5177</v>
+        <v>-1.5738</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.5177</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4438</v>
+        <v>-4.6878</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4255</v>
+        <v>-2.8172</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0183</v>
+        <v>-1.8706</v>
       </c>
       <c r="G9" t="n">
         <v>-4.2962</v>
@@ -1156,13 +1156,13 @@
         <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2589</v>
+        <v>0.0149</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5397</v>
+        <v>0.148</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2808</v>
+        <v>-0.1331</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8888</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.7748</v>
+        <v>-4.9919</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5771</v>
+        <v>-3.6958</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1976</v>
+        <v>-1.2961</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6052</v>
@@ -1234,13 +1234,13 @@
         <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.502</v>
+        <v>-0.7191</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9849</v>
+        <v>-0.1035</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5171</v>
+        <v>-0.6156</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5725</v>
+        <v>-5.5675</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2219</v>
+        <v>-4.4385</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3506</v>
+        <v>-1.129</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4826</v>
@@ -1312,13 +1312,13 @@
         <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0523</v>
+        <v>-0.0473</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7113</v>
+        <v>0.0721</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.341</v>
+        <v>-0.1194</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6289</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2211</v>
+        <v>-6.0196</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3222</v>
+        <v>-4.4409</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8988</v>
+        <v>-1.5788</v>
       </c>
       <c r="G12" t="n">
         <v>-4.348</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9466</v>
+        <v>-0.7452</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1826</v>
+        <v>-0.3012</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.764</v>
+        <v>-0.444</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.167400000000001</v>
+        <v>-6.7203</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3841</v>
+        <v>-4.4048</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7834</v>
+        <v>-2.3155</v>
       </c>
       <c r="G13" t="n">
         <v>-4.7533</v>
@@ -1468,13 +1468,13 @@
         <v>1.4823</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7847</v>
+        <v>-0.3376</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2373</v>
+        <v>-0.258</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5474</v>
+        <v>-0.0796</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2589</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-32.7099</v>
+        <v>-32.857</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.4004</v>
+        <v>-17.4984</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.3094</v>
+        <v>-15.3588</v>
       </c>
       <c r="G14" t="n">
         <v>-18.8694</v>
@@ -1516,7 +1516,7 @@
         <v>-19.0074</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1380999999999999</v>
+        <v>0.1381000000000003</v>
       </c>
       <c r="J14" t="n">
         <v>-1.182699999999999</v>
@@ -1546,13 +1546,13 @@
         <v>11.8583</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8573999999999993</v>
+        <v>-1.0045</v>
       </c>
       <c r="T14" t="n">
-        <v>1.072099999999999</v>
+        <v>0.9742000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.9294</v>
+        <v>-1.9787</v>
       </c>
       <c r="V14" t="n">
         <v>-7.239199999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.9024</v>
+        <v>9.1844</v>
       </c>
       <c r="E15" t="n">
-        <v>8.5114</v>
+        <v>5.8674</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3909</v>
+        <v>3.3171</v>
       </c>
       <c r="G15" t="n">
         <v>5.3603</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1328</v>
+        <v>1.4148</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7157</v>
+        <v>1.0716</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4171</v>
+        <v>0.3432</v>
       </c>
       <c r="V15" t="n">
         <v>0.0005</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9779</v>
+        <v>4.6266</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2073</v>
+        <v>1.4601</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7706</v>
+        <v>3.1665</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2543</v>
+        <v>4.3773</v>
       </c>
       <c r="H16" t="n">
-        <v>4.0621</v>
+        <v>1.1856</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1922</v>
+        <v>3.1917</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3537</v>
+        <v>3.8744</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5242</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8294</v>
+        <v>3.1531</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9006</v>
+        <v>0.5029</v>
       </c>
       <c r="N16" t="n">
-        <v>1.5379</v>
+        <v>0.4643</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6373</v>
+        <v>0.0386</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0382</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.891</v>
+        <v>-2.9646</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8529</v>
+        <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5024</v>
+        <v>0.6199</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.5503</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7016</v>
+        <v>0.0696</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2594</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7657</v>
+        <v>4.3143</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6559</v>
+        <v>1.0115</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1098</v>
+        <v>3.3028</v>
       </c>
       <c r="G17" t="n">
-        <v>4.3773</v>
+        <v>4.2543</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1856</v>
+        <v>4.0621</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1917</v>
+        <v>0.1922</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8744</v>
+        <v>3.3537</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7213000000000001</v>
+        <v>2.5242</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1531</v>
+        <v>0.8294</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5029</v>
+        <v>0.9006</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4643</v>
+        <v>1.5379</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0386</v>
+        <v>-0.6373</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3706</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9646</v>
+        <v>-3.891</v>
       </c>
       <c r="R17" t="n">
-        <v>2.594</v>
+        <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>0.759</v>
+        <v>0.8388</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7461</v>
+        <v>0.605</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0129</v>
+        <v>0.2338</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2594</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7079</v>
+        <v>3.8051</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3567</v>
+        <v>2.0664</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3512</v>
+        <v>1.7387</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1049</v>
+        <v>1.8094</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0395</v>
+        <v>2.6265</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1444</v>
+        <v>-0.8171</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5297</v>
+        <v>1.3851</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0226</v>
+        <v>1.872</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5071</v>
+        <v>-0.487</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4247</v>
+        <v>0.4243</v>
       </c>
       <c r="N18" t="n">
-        <v>1.062</v>
+        <v>0.7544</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6373</v>
+        <v>-0.3301</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.4823</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4087</v>
+        <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.199</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0373</v>
+        <v>0.3669</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8321</v>
+        <v>-0.1679</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4621</v>
+        <v>0.3144</v>
       </c>
       <c r="W18" t="n">
-        <v>3.7766</v>
+        <v>0.3144</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6523</v>
+        <v>3.4686</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2829</v>
+        <v>0.4547</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3694</v>
+        <v>3.0139</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8094</v>
+        <v>-1.1049</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6265</v>
+        <v>0.0395</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8171</v>
+        <v>-1.1444</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3851</v>
+        <v>-1.5297</v>
       </c>
       <c r="K19" t="n">
-        <v>1.872</v>
+        <v>-1.0226</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.487</v>
+        <v>-0.5071</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4243</v>
+        <v>0.4247</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7544</v>
+        <v>1.062</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3301</v>
+        <v>-0.6373</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4823</v>
+        <v>2.4087</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9538</v>
+        <v>0.5555</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4166</v>
+        <v>0.0606</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5372</v>
+        <v>0.4949</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3144</v>
+        <v>3.4621</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3144</v>
+        <v>3.7766</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. MERINO LUQUE</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4836</v>
+        <v>2.9816</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7142</v>
+        <v>1.5529</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2306</v>
+        <v>1.4287</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6158</v>
+        <v>1.1396</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2594</v>
+        <v>1.0028</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3564</v>
+        <v>0.1367</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4278</v>
+        <v>1.6955</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7642</v>
+        <v>1.0521</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6635</v>
+        <v>0.6434</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.556</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5048</v>
+        <v>-0.0493</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3071</v>
+        <v>-0.5067</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1117</v>
+        <v>2.594</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8177</v>
+        <v>-0.8991</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6019</v>
+        <v>-0.2897</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2159</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5738</v>
+        <v>1.2589</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8883</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>R. MERINO LUQUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8214</v>
+        <v>2.8593</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7695</v>
+        <v>2.9101</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0519</v>
+        <v>-0.0508</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1396</v>
+        <v>0.6158</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0028</v>
+        <v>0.2594</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1367</v>
+        <v>0.3564</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6955</v>
+        <v>1.4278</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0521</v>
+        <v>0.7642</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6434</v>
+        <v>0.6635</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.556</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0493</v>
+        <v>-0.5048</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5067</v>
+        <v>-0.3071</v>
       </c>
       <c r="P21" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.594</v>
+        <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0593</v>
+        <v>-0.4421</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0732</v>
+        <v>-0.406</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9861</v>
+        <v>-0.0361</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2589</v>
+        <v>1.5738</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2589</v>
+        <v>1.8883</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.1575</v>
+        <v>2.71</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.253</v>
+        <v>0.8243</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4104</v>
+        <v>1.8857</v>
       </c>
       <c r="G22" t="n">
         <v>3.1494</v>
@@ -2170,13 +2170,13 @@
         <v>2.7793</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1031</v>
+        <v>-0.5506</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.052</v>
+        <v>0.0252</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0511</v>
+        <v>-0.5758</v>
       </c>
       <c r="V22" t="n">
         <v>-0.63</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6181</v>
+        <v>-0.4463</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7855</v>
+        <v>-0.6876</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1674</v>
+        <v>0.2413</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5368000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>0.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2666</v>
+        <v>-0.0948</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0547</v>
+        <v>0.0432</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2119</v>
+        <v>-0.138</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>32.8506</v>
+        <v>33.5036</v>
       </c>
       <c r="E24" t="n">
-        <v>15.4594</v>
+        <v>15.4598</v>
       </c>
       <c r="F24" t="n">
-        <v>17.391</v>
+        <v>18.0439</v>
       </c>
       <c r="G24" t="n">
         <v>19.0644</v>
@@ -2314,7 +2314,7 @@
         <v>4.555800000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.4163</v>
+        <v>-3.416300000000001</v>
       </c>
       <c r="P24" t="n">
         <v>5.5585</v>
@@ -2326,16 +2326,16 @@
         <v>17.6022</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9886000000000004</v>
+        <v>1.6414</v>
       </c>
       <c r="T24" t="n">
-        <v>2.027000000000001</v>
+        <v>2.0271</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0385</v>
+        <v>-0.3857</v>
       </c>
       <c r="V24" t="n">
-        <v>7.2391</v>
+        <v>7.239100000000001</v>
       </c>
       <c r="W24" t="n">
         <v>7.551600000000001</v>
